--- a/Lab/Excel+LAB+1+Dataset_Dmart(1).xlsx
+++ b/Lab/Excel+LAB+1+Dataset_Dmart(1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6800"/>
+    <workbookView windowWidth="19200" windowHeight="6800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4532,7 +4532,7 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="48">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -4765,6 +4765,20 @@
       <font>
         <name val="Calibri"/>
         <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -5014,25 +5028,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="36"/>
-      <tableStyleElement type="headerRow" dxfId="35"/>
-      <tableStyleElement type="totalRow" dxfId="34"/>
-      <tableStyleElement type="firstColumn" dxfId="33"/>
-      <tableStyleElement type="lastColumn" dxfId="32"/>
-      <tableStyleElement type="firstRowStripe" dxfId="31"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="30"/>
+      <tableStyleElement type="wholeTable" dxfId="37"/>
+      <tableStyleElement type="headerRow" dxfId="36"/>
+      <tableStyleElement type="totalRow" dxfId="35"/>
+      <tableStyleElement type="firstColumn" dxfId="34"/>
+      <tableStyleElement type="lastColumn" dxfId="33"/>
+      <tableStyleElement type="firstRowStripe" dxfId="32"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="31"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="46"/>
-      <tableStyleElement type="totalRow" dxfId="45"/>
-      <tableStyleElement type="firstRowStripe" dxfId="44"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="43"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="42"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="41"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="40"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="39"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="38"/>
-      <tableStyleElement type="pageFieldValues" dxfId="37"/>
+      <tableStyleElement type="headerRow" dxfId="47"/>
+      <tableStyleElement type="totalRow" dxfId="46"/>
+      <tableStyleElement type="firstRowStripe" dxfId="45"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="44"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="43"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="42"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="41"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="40"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="39"/>
+      <tableStyleElement type="pageFieldValues" dxfId="38"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -5102,25 +5116,25 @@
       <calculatedColumnFormula>SECOND(R2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" name="Monthly_Sales" dataDxfId="21"/>
-    <tableColumn id="23" name="Column2"/>
-    <tableColumn id="17" name="Target" dataDxfId="22"/>
-    <tableColumn id="30" name="Column1" dataDxfId="23">
+    <tableColumn id="23" name="Column2" dataDxfId="22"/>
+    <tableColumn id="17" name="Target" dataDxfId="23"/>
+    <tableColumn id="30" name="Column1" dataDxfId="24">
       <calculatedColumnFormula>IF(X2&gt;50000,"Highe Target","Low Target")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" name="Column5" dataDxfId="24">
+    <tableColumn id="31" name="Column5" dataDxfId="25">
       <calculatedColumnFormula>IF(NOT(X2&lt;50000),"Highe target","Lower Target")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" name="Column6" dataDxfId="25">
+    <tableColumn id="32" name="Column6" dataDxfId="26">
       <calculatedColumnFormula array="1">_xlfn.IFS(X2&lt;60000,"LOWERTarget",X2&lt;80000,"Medium Target",X2,"Highe Target")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" name="Customer_Feedback" dataDxfId="26"/>
-    <tableColumn id="20" name="Upper" dataDxfId="27">
+    <tableColumn id="18" name="Customer_Feedback" dataDxfId="27"/>
+    <tableColumn id="20" name="Upper" dataDxfId="28">
       <calculatedColumnFormula>UPPER(AB2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" name="Lower" dataDxfId="28">
+    <tableColumn id="21" name="Lower" dataDxfId="29">
       <calculatedColumnFormula>LOWER(AB2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" name="Propar" dataDxfId="29">
+    <tableColumn id="22" name="Propar" dataDxfId="30">
       <calculatedColumnFormula>PROPER(AB2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7348,7 +7362,7 @@
       </c>
       <c r="AJ16" s="13">
         <f ca="1">NOW()</f>
-        <v>46258.5392708333</v>
+        <v>46260.8530324074</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:36">
@@ -7470,7 +7484,7 @@
       </c>
       <c r="AJ17" s="14">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:36">

--- a/Lab/Excel+LAB+1+Dataset_Dmart(1).xlsx
+++ b/Lab/Excel+LAB+1+Dataset_Dmart(1).xlsx
@@ -4778,7 +4778,7 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="AJ16" s="13">
         <f ca="1">NOW()</f>
-        <v>46260.8530324074</v>
+        <v>46267.483912037</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:36">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="AJ17" s="14">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:36">
